--- a/Team-Data/2007-08/3-31-2007-08.xlsx
+++ b/Team-Data/2007-08/3-31-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,85 +728,85 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" t="n">
         <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>0.459</v>
+        <v>0.452</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J2" t="n">
         <v>79.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.452</v>
+        <v>0.45</v>
       </c>
       <c r="L2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="M2" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="O2" t="n">
         <v>21.1</v>
       </c>
       <c r="P2" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.774</v>
+        <v>0.772</v>
       </c>
       <c r="R2" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S2" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T2" t="n">
-        <v>42.2</v>
+        <v>42.4</v>
       </c>
       <c r="U2" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V2" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W2" t="n">
         <v>7.4</v>
       </c>
       <c r="X2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA2" t="n">
         <v>21.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.59999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.6</v>
+        <v>-1.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -751,10 +818,10 @@
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ2" t="n">
         <v>23</v>
@@ -769,10 +836,10 @@
         <v>28</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP2" t="n">
         <v>7</v>
@@ -781,7 +848,7 @@
         <v>7</v>
       </c>
       <c r="AR2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
@@ -793,7 +860,7 @@
         <v>12</v>
       </c>
       <c r="AV2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW2" t="n">
         <v>14</v>
@@ -802,16 +869,16 @@
         <v>3</v>
       </c>
       <c r="AY2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC2" t="n">
         <v>18</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>10.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -960,7 +1027,7 @@
         <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
         <v>24</v>
@@ -969,7 +1036,7 @@
         <v>9</v>
       </c>
       <c r="AT3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AU3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E4" t="n">
         <v>28</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>0.378</v>
+        <v>0.384</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1043,7 +1110,7 @@
         <v>35.7</v>
       </c>
       <c r="J4" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
       <c r="K4" t="n">
         <v>0.447</v>
@@ -1052,19 +1119,19 @@
         <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.366</v>
+        <v>0.367</v>
       </c>
       <c r="O4" t="n">
         <v>18.1</v>
       </c>
       <c r="P4" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.71</v>
+        <v>0.709</v>
       </c>
       <c r="R4" t="n">
         <v>10.9</v>
@@ -1079,7 +1146,7 @@
         <v>21.1</v>
       </c>
       <c r="V4" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W4" t="n">
         <v>7.6</v>
@@ -1088,7 +1155,7 @@
         <v>4.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z4" t="n">
         <v>22</v>
@@ -1097,13 +1164,13 @@
         <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>96</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>-4.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
@@ -1115,7 +1182,7 @@
         <v>23</v>
       </c>
       <c r="AH4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="n">
         <v>26</v>
@@ -1124,7 +1191,7 @@
         <v>20</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
         <v>16</v>
@@ -1154,7 +1221,7 @@
         <v>26</v>
       </c>
       <c r="AU4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV4" t="n">
         <v>20</v>
@@ -1163,7 +1230,7 @@
         <v>12</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY4" t="n">
         <v>30</v>
@@ -1172,10 +1239,10 @@
         <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1300,7 +1367,7 @@
         <v>10</v>
       </c>
       <c r="AI5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
@@ -1318,13 +1385,13 @@
         <v>14</v>
       </c>
       <c r="AO5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP5" t="n">
         <v>16</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
@@ -1342,7 +1409,7 @@
         <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
         <v>7</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1479,22 +1546,22 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL6" t="n">
         <v>12</v>
       </c>
       <c r="AM6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN6" t="n">
         <v>15</v>
@@ -1512,13 +1579,13 @@
         <v>3</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
         <v>2</v>
       </c>
       <c r="AU6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV6" t="n">
         <v>10</v>
@@ -1542,7 +1609,7 @@
         <v>20</v>
       </c>
       <c r="BC6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -1571,22 +1638,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F7" t="n">
         <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>0.622</v>
+        <v>0.616</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J7" t="n">
         <v>79</v>
@@ -1601,25 +1668,25 @@
         <v>17</v>
       </c>
       <c r="N7" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O7" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="P7" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S7" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T7" t="n">
-        <v>43</v>
+        <v>43.2</v>
       </c>
       <c r="U7" t="n">
         <v>20.7</v>
@@ -1628,13 +1695,13 @@
         <v>13.1</v>
       </c>
       <c r="W7" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="X7" t="n">
         <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z7" t="n">
         <v>22</v>
@@ -1643,13 +1710,13 @@
         <v>21.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>100</v>
+        <v>100.1</v>
       </c>
       <c r="AC7" t="n">
         <v>4.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE7" t="n">
         <v>10</v>
@@ -1661,7 +1728,7 @@
         <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>16</v>
@@ -1679,7 +1746,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO7" t="n">
         <v>7</v>
@@ -1688,16 +1755,16 @@
         <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR7" t="n">
         <v>21</v>
       </c>
       <c r="AS7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT7" t="n">
         <v>7</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8</v>
       </c>
       <c r="AU7" t="n">
         <v>21</v>
@@ -1712,16 +1779,16 @@
         <v>11</v>
       </c>
       <c r="AY7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA7" t="n">
         <v>14</v>
       </c>
       <c r="BB7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
         <v>9</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -1753,64 +1820,64 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E8" t="n">
         <v>45</v>
       </c>
       <c r="F8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>0.608</v>
+        <v>0.616</v>
       </c>
       <c r="H8" t="n">
         <v>48.3</v>
       </c>
       <c r="I8" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="J8" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.468</v>
+        <v>0.467</v>
       </c>
       <c r="L8" t="n">
         <v>6.9</v>
       </c>
       <c r="M8" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N8" t="n">
         <v>0.357</v>
       </c>
       <c r="O8" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="P8" t="n">
         <v>30.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.754</v>
+        <v>0.756</v>
       </c>
       <c r="R8" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S8" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T8" t="n">
-        <v>43.9</v>
+        <v>44.1</v>
       </c>
       <c r="U8" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="V8" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X8" t="n">
         <v>6.8</v>
@@ -1819,37 +1886,37 @@
         <v>4.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA8" t="n">
         <v>23.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>109.8</v>
+        <v>109.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI8" t="n">
         <v>4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK8" t="n">
         <v>7</v>
@@ -1858,7 +1925,7 @@
         <v>13</v>
       </c>
       <c r="AM8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN8" t="n">
         <v>16</v>
@@ -1870,13 +1937,13 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT8" t="n">
         <v>5</v>
@@ -1885,7 +1952,7 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>7.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2043,7 +2110,7 @@
         <v>21</v>
       </c>
       <c r="AN9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO9" t="n">
         <v>19</v>
@@ -2058,25 +2125,25 @@
         <v>11</v>
       </c>
       <c r="AS9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ9" t="n">
         <v>11</v>
@@ -2085,7 +2152,7 @@
         <v>25</v>
       </c>
       <c r="BB9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -2195,16 +2262,16 @@
         <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF10" t="n">
         <v>10</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH10" t="n">
         <v>17</v>
@@ -2225,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO10" t="n">
         <v>13</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -2377,16 +2444,16 @@
         <v>4.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF11" t="n">
         <v>5</v>
       </c>
       <c r="AG11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
         <v>24</v>
@@ -2395,7 +2462,7 @@
         <v>15</v>
       </c>
       <c r="AJ11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AK11" t="n">
         <v>17</v>
@@ -2410,7 +2477,7 @@
         <v>27</v>
       </c>
       <c r="AO11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP11" t="n">
         <v>26</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" t="n">
         <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>0.419</v>
+        <v>0.411</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J12" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="K12" t="n">
         <v>0.443</v>
@@ -2514,19 +2581,19 @@
         <v>0.374</v>
       </c>
       <c r="O12" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P12" t="n">
         <v>24.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.772</v>
+        <v>0.77</v>
       </c>
       <c r="R12" t="n">
         <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T12" t="n">
         <v>43.2</v>
@@ -2538,7 +2605,7 @@
         <v>15</v>
       </c>
       <c r="W12" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X12" t="n">
         <v>5</v>
@@ -2556,19 +2623,19 @@
         <v>104</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.8</v>
+        <v>-2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF12" t="n">
         <v>20</v>
       </c>
       <c r="AG12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH12" t="n">
         <v>22</v>
@@ -2577,7 +2644,7 @@
         <v>9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK12" t="n">
         <v>25</v>
@@ -2598,7 +2665,7 @@
         <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
         <v>17</v>
@@ -2607,10 +2674,10 @@
         <v>8</v>
       </c>
       <c r="AT12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU12" t="n">
         <v>7</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8</v>
       </c>
       <c r="AV12" t="n">
         <v>25</v>
@@ -2622,7 +2689,7 @@
         <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -2663,25 +2730,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E13" t="n">
         <v>22</v>
       </c>
       <c r="F13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>0.297</v>
+        <v>0.301</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="J13" t="n">
-        <v>78.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="K13" t="n">
         <v>0.439</v>
@@ -2693,31 +2760,31 @@
         <v>13.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.322</v>
+        <v>0.32</v>
       </c>
       <c r="O13" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="P13" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="R13" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S13" t="n">
         <v>30.2</v>
       </c>
       <c r="T13" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="U13" t="n">
         <v>21.1</v>
       </c>
       <c r="V13" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W13" t="n">
         <v>6.9</v>
@@ -2735,13 +2802,13 @@
         <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>94</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC13" t="n">
         <v>-6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2753,7 +2820,7 @@
         <v>25</v>
       </c>
       <c r="AH13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI13" t="n">
         <v>30</v>
@@ -2762,7 +2829,7 @@
         <v>28</v>
       </c>
       <c r="AK13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL13" t="n">
         <v>28</v>
@@ -2774,16 +2841,16 @@
         <v>29</v>
       </c>
       <c r="AO13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP13" t="n">
         <v>8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS13" t="n">
         <v>18</v>
@@ -2792,7 +2859,7 @@
         <v>29</v>
       </c>
       <c r="AU13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AV13" t="n">
         <v>12</v>
@@ -2810,7 +2877,7 @@
         <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>4</v>
@@ -2935,7 +3002,7 @@
         <v>5</v>
       </c>
       <c r="AH14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
@@ -2950,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="AM14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN14" t="n">
         <v>7</v>
@@ -2989,16 +3056,16 @@
         <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
         <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" t="n">
         <v>19</v>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>0.257</v>
+        <v>0.26</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
@@ -3048,7 +3115,7 @@
         <v>81.8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L15" t="n">
         <v>7.4</v>
@@ -3060,37 +3127,37 @@
         <v>0.349</v>
       </c>
       <c r="O15" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P15" t="n">
         <v>25.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.729</v>
+        <v>0.732</v>
       </c>
       <c r="R15" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S15" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="T15" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U15" t="n">
         <v>19.1</v>
       </c>
       <c r="V15" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="W15" t="n">
         <v>6.1</v>
       </c>
       <c r="X15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z15" t="n">
         <v>19.6</v>
@@ -3102,10 +3169,10 @@
         <v>100.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.2</v>
+        <v>-6</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,13 +3184,13 @@
         <v>28</v>
       </c>
       <c r="AH15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK15" t="n">
         <v>15</v>
@@ -3138,22 +3205,22 @@
         <v>22</v>
       </c>
       <c r="AO15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP15" t="n">
         <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
         <v>22</v>
       </c>
       <c r="AS15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU15" t="n">
         <v>29</v>
@@ -3174,7 +3241,7 @@
         <v>5</v>
       </c>
       <c r="BA15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
         <v>11</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -3209,46 +3276,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E16" t="n">
         <v>13</v>
       </c>
       <c r="F16" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
-        <v>0.176</v>
+        <v>0.178</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="J16" t="n">
-        <v>77.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0.447</v>
       </c>
       <c r="L16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="M16" t="n">
         <v>15.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0.349</v>
+        <v>0.346</v>
       </c>
       <c r="O16" t="n">
         <v>17.3</v>
       </c>
       <c r="P16" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.725</v>
+        <v>0.726</v>
       </c>
       <c r="R16" t="n">
         <v>9.1</v>
@@ -3263,13 +3330,13 @@
         <v>20</v>
       </c>
       <c r="V16" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W16" t="n">
         <v>7.2</v>
       </c>
       <c r="X16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y16" t="n">
         <v>4</v>
@@ -3278,16 +3345,16 @@
         <v>20.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>91.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3299,7 +3366,7 @@
         <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI16" t="n">
         <v>29</v>
@@ -3311,7 +3378,7 @@
         <v>22</v>
       </c>
       <c r="AL16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM16" t="n">
         <v>24</v>
@@ -3341,13 +3408,13 @@
         <v>24</v>
       </c>
       <c r="AV16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW16" t="n">
         <v>16</v>
       </c>
       <c r="AX16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY16" t="n">
         <v>4</v>
@@ -3362,7 +3429,7 @@
         <v>30</v>
       </c>
       <c r="BC16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3560,7 @@
         <v>23</v>
       </c>
       <c r="AL17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM17" t="n">
         <v>22</v>
@@ -3517,7 +3584,7 @@
         <v>30</v>
       </c>
       <c r="AT17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU17" t="n">
         <v>20</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3733,7 @@
         <v>29</v>
       </c>
       <c r="AI18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>9</v>
@@ -3705,7 +3772,7 @@
         <v>26</v>
       </c>
       <c r="AV18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW18" t="n">
         <v>13</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
@@ -3845,7 +3912,7 @@
         <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AI19" t="n">
         <v>28</v>
@@ -3872,7 +3939,7 @@
         <v>4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR19" t="n">
         <v>16</v>
@@ -3887,7 +3954,7 @@
         <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
         <v>25</v>
@@ -3902,7 +3969,7 @@
         <v>26</v>
       </c>
       <c r="BA19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB19" t="n">
         <v>25</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4100,7 @@
         <v>6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK20" t="n">
         <v>8</v>
@@ -4054,10 +4121,10 @@
         <v>29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS20" t="n">
         <v>15</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-6.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4230,7 +4297,7 @@
         <v>28</v>
       </c>
       <c r="AO21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP21" t="n">
         <v>11</v>
@@ -4239,7 +4306,7 @@
         <v>27</v>
       </c>
       <c r="AR21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS21" t="n">
         <v>22</v>
@@ -4260,7 +4327,7 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ21" t="n">
         <v>19</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>4.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE22" t="n">
         <v>9</v>
@@ -4391,10 +4458,10 @@
         <v>9</v>
       </c>
       <c r="AH22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ22" t="n">
         <v>26</v>
@@ -4433,7 +4500,7 @@
         <v>22</v>
       </c>
       <c r="AV22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW22" t="n">
         <v>27</v>
@@ -4442,19 +4509,19 @@
         <v>25</v>
       </c>
       <c r="AY22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB22" t="n">
         <v>6</v>
       </c>
       <c r="BC22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -4561,10 +4628,10 @@
         <v>0.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF23" t="n">
         <v>17</v>
@@ -4573,7 +4640,7 @@
         <v>17</v>
       </c>
       <c r="AH23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
         <v>10</v>
@@ -4594,7 +4661,7 @@
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP23" t="n">
         <v>10</v>
@@ -4615,7 +4682,7 @@
         <v>23</v>
       </c>
       <c r="AV23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E24" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F24" t="n">
         <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>0.676</v>
+        <v>0.671</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
@@ -4683,49 +4750,49 @@
         <v>41.4</v>
       </c>
       <c r="J24" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K24" t="n">
-        <v>0.499</v>
+        <v>0.5</v>
       </c>
       <c r="L24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="O24" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="P24" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="R24" t="n">
         <v>8.6</v>
       </c>
-      <c r="M24" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="O24" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="P24" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0.786</v>
-      </c>
-      <c r="R24" t="n">
-        <v>8.699999999999999</v>
-      </c>
       <c r="S24" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T24" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U24" t="n">
         <v>26.8</v>
       </c>
       <c r="V24" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W24" t="n">
         <v>6.6</v>
       </c>
       <c r="X24" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Y24" t="n">
         <v>3.8</v>
@@ -4737,31 +4804,31 @@
         <v>21</v>
       </c>
       <c r="AB24" t="n">
-        <v>110.2</v>
+        <v>109.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF24" t="n">
         <v>5</v>
       </c>
       <c r="AG24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI24" t="n">
         <v>2</v>
       </c>
       <c r="AJ24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK24" t="n">
         <v>1</v>
@@ -4776,7 +4843,7 @@
         <v>3</v>
       </c>
       <c r="AO24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AP24" t="n">
         <v>21</v>
@@ -4788,7 +4855,7 @@
         <v>30</v>
       </c>
       <c r="AS24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT24" t="n">
         <v>22</v>
@@ -4806,19 +4873,19 @@
         <v>2</v>
       </c>
       <c r="AY24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ24" t="n">
         <v>9</v>
       </c>
       <c r="BA24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB24" t="n">
         <v>2</v>
       </c>
       <c r="BC24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -4925,19 +4992,19 @@
         <v>-0.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
       </c>
       <c r="AF25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI25" t="n">
         <v>25</v>
@@ -4979,7 +5046,7 @@
         <v>16</v>
       </c>
       <c r="AV25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW25" t="n">
         <v>30</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -5107,16 +5174,16 @@
         <v>-2.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF26" t="n">
         <v>18</v>
       </c>
       <c r="AG26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH26" t="n">
         <v>6</v>
@@ -5137,7 +5204,7 @@
         <v>19</v>
       </c>
       <c r="AN26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO26" t="n">
         <v>2</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
         <v>3</v>
@@ -5301,7 +5368,7 @@
         <v>4</v>
       </c>
       <c r="AH27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI27" t="n">
         <v>24</v>
@@ -5319,7 +5386,7 @@
         <v>8</v>
       </c>
       <c r="AN27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO27" t="n">
         <v>26</v>
@@ -5340,7 +5407,7 @@
         <v>20</v>
       </c>
       <c r="AU27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV27" t="n">
         <v>4</v>
@@ -5358,7 +5425,7 @@
         <v>2</v>
       </c>
       <c r="BA27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB27" t="n">
         <v>24</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-8.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
         <v>29</v>
@@ -5483,7 +5550,7 @@
         <v>29</v>
       </c>
       <c r="AH28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
@@ -5492,7 +5559,7 @@
         <v>4</v>
       </c>
       <c r="AK28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL28" t="n">
         <v>29</v>
@@ -5516,7 +5583,7 @@
         <v>10</v>
       </c>
       <c r="AS28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT28" t="n">
         <v>3</v>
@@ -5537,7 +5604,7 @@
         <v>26</v>
       </c>
       <c r="AZ28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA28" t="n">
         <v>26</v>
@@ -5546,7 +5613,7 @@
         <v>15</v>
       </c>
       <c r="BC28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E29" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F29" t="n">
         <v>36</v>
       </c>
       <c r="G29" t="n">
-        <v>0.514</v>
+        <v>0.507</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
@@ -5599,22 +5666,22 @@
         <v>0.468</v>
       </c>
       <c r="L29" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M29" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.4</v>
+        <v>0.401</v>
       </c>
       <c r="O29" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="P29" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="R29" t="n">
         <v>9.5</v>
@@ -5632,19 +5699,19 @@
         <v>11.8</v>
       </c>
       <c r="W29" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X29" t="n">
         <v>4</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z29" t="n">
         <v>19.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AB29" t="n">
         <v>100.1</v>
@@ -5653,25 +5720,25 @@
         <v>2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI29" t="n">
         <v>7</v>
       </c>
       <c r="AJ29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK29" t="n">
         <v>6</v>
@@ -5692,10 +5759,10 @@
         <v>30</v>
       </c>
       <c r="AQ29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS29" t="n">
         <v>14</v>
@@ -5725,7 +5792,7 @@
         <v>29</v>
       </c>
       <c r="BB29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC29" t="n">
         <v>13</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -5757,67 +5824,67 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E30" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F30" t="n">
         <v>26</v>
       </c>
       <c r="G30" t="n">
-        <v>0.653</v>
+        <v>0.649</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
       </c>
       <c r="I30" t="n">
-        <v>40.2</v>
+        <v>40</v>
       </c>
       <c r="J30" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.499</v>
+        <v>0.498</v>
       </c>
       <c r="L30" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="M30" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0.373</v>
+        <v>0.368</v>
       </c>
       <c r="O30" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="P30" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="R30" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S30" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="T30" t="n">
         <v>40.7</v>
       </c>
       <c r="U30" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="V30" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W30" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y30" t="n">
         <v>5.2</v>
@@ -5826,19 +5893,19 @@
         <v>24.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>107</v>
+        <v>106.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF30" t="n">
         <v>8</v>
@@ -5865,7 +5932,7 @@
         <v>27</v>
       </c>
       <c r="AN30" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5895,22 +5962,22 @@
         <v>3</v>
       </c>
       <c r="AX30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ30" t="n">
         <v>30</v>
       </c>
       <c r="BA30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB30" t="n">
         <v>5</v>
       </c>
       <c r="BC30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
@@ -5939,31 +6006,31 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E31" t="n">
         <v>38</v>
       </c>
       <c r="F31" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G31" t="n">
-        <v>0.514</v>
+        <v>0.521</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J31" t="n">
-        <v>81.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K31" t="n">
         <v>0.444</v>
       </c>
       <c r="L31" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M31" t="n">
         <v>19.5</v>
@@ -5978,16 +6045,16 @@
         <v>24.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="R31" t="n">
         <v>12.1</v>
       </c>
       <c r="S31" t="n">
-        <v>29.3</v>
+        <v>29.5</v>
       </c>
       <c r="T31" t="n">
-        <v>41.4</v>
+        <v>41.6</v>
       </c>
       <c r="U31" t="n">
         <v>19.4</v>
@@ -6011,13 +6078,13 @@
         <v>20.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6032,10 +6099,10 @@
         <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AK31" t="n">
         <v>24</v>
@@ -6056,16 +6123,16 @@
         <v>19</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR31" t="n">
         <v>9</v>
       </c>
       <c r="AS31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AU31" t="n">
         <v>27</v>
@@ -6086,13 +6153,13 @@
         <v>6</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>14</v>
       </c>
       <c r="BC31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-31-2007-08</t>
+          <t>2008-03-31</t>
         </is>
       </c>
     </row>
